--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124661457</v>
       </c>
       <c r="B2" t="n">
-        <v>74840</v>
+        <v>74964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>126721331</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126721327</v>
       </c>
       <c r="B4" t="n">
-        <v>98359</v>
+        <v>98434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126721325</v>
+        <v>126721329</v>
       </c>
       <c r="B5" t="n">
-        <v>98278</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632753</v>
+        <v>632585</v>
       </c>
       <c r="R5" t="n">
-        <v>6898803</v>
+        <v>6898509</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126721332</v>
+        <v>126721325</v>
       </c>
       <c r="B6" t="n">
-        <v>98384</v>
+        <v>98353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632751</v>
+        <v>632753</v>
       </c>
       <c r="R6" t="n">
-        <v>6898784</v>
+        <v>6898803</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126721329</v>
+        <v>126721332</v>
       </c>
       <c r="B7" t="n">
-        <v>98395</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632585</v>
+        <v>632751</v>
       </c>
       <c r="R7" t="n">
-        <v>6898509</v>
+        <v>6898784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,7 +1280,7 @@
         <v>126721330</v>
       </c>
       <c r="B8" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>126721324</v>
       </c>
       <c r="B9" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>126721331</v>
       </c>
       <c r="B3" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126721327</v>
       </c>
       <c r="B4" t="n">
-        <v>98434</v>
+        <v>98440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126721329</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126721325</v>
       </c>
       <c r="B6" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126721332</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>126721330</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>126721324</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>126721331</v>
       </c>
       <c r="B3" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126721327</v>
       </c>
       <c r="B4" t="n">
-        <v>98440</v>
+        <v>98441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126721329</v>
       </c>
       <c r="B5" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126721325</v>
       </c>
       <c r="B6" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126721332</v>
       </c>
       <c r="B7" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>126721330</v>
       </c>
       <c r="B8" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>126721324</v>
       </c>
       <c r="B9" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>126721324</v>
       </c>
       <c r="B9" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>126721324</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1474,6 +1474,103 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128302733</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ennsikslandet, Ennsikslandet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>632668</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6898566</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>128302733</v>
       </c>
       <c r="B10" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>128302733</v>
       </c>
       <c r="B10" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>128302733</v>
       </c>
       <c r="B10" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>128302733</v>
       </c>
       <c r="B10" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>128302733</v>
       </c>
       <c r="B10" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -1479,7 +1479,7 @@
         <v>128302733</v>
       </c>
       <c r="B10" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>126721331</v>
       </c>
       <c r="B3" t="n">
-        <v>98464</v>
+        <v>98457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126721327</v>
       </c>
       <c r="B4" t="n">
-        <v>98441</v>
+        <v>98434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126721329</v>
       </c>
       <c r="B5" t="n">
-        <v>98477</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126721325</v>
       </c>
       <c r="B6" t="n">
-        <v>98360</v>
+        <v>98353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126721332</v>
       </c>
       <c r="B7" t="n">
-        <v>98466</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>126721330</v>
       </c>
       <c r="B8" t="n">
-        <v>98477</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>126721324</v>
       </c>
       <c r="B9" t="n">
-        <v>98471</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124661457</v>
+        <v>124662148</v>
       </c>
       <c r="B2" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632989</v>
+        <v>632692</v>
       </c>
       <c r="R2" t="n">
-        <v>6898628</v>
+        <v>6898831</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt på flera träd</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126721331</v>
+        <v>126721327</v>
       </c>
       <c r="B3" t="n">
-        <v>98464</v>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>620</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632992</v>
+        <v>632608</v>
       </c>
       <c r="R3" t="n">
-        <v>6898452</v>
+        <v>6898526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126721327</v>
+        <v>124661379</v>
       </c>
       <c r="B4" t="n">
-        <v>98441</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>620</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632608</v>
+        <v>632998</v>
       </c>
       <c r="R4" t="n">
-        <v>6898526</v>
+        <v>6898651</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,60 +974,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126721329</v>
+        <v>128302733</v>
       </c>
       <c r="B5" t="n">
-        <v>98477</v>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkön, Mpd</t>
+          <t>Ennsikslandet, Ennsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632585</v>
+        <v>632668</v>
       </c>
       <c r="R5" t="n">
-        <v>6898509</v>
+        <v>6898566</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126721325</v>
+        <v>124662316</v>
       </c>
       <c r="B6" t="n">
-        <v>98360</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,37 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björkön, Mpd</t>
+          <t>Björkön, Björkön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632753</v>
+        <v>632692</v>
       </c>
       <c r="R6" t="n">
-        <v>6898803</v>
+        <v>6898831</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,12 +1148,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,57 +1178,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126721332</v>
+        <v>124661457</v>
       </c>
       <c r="B7" t="n">
-        <v>98466</v>
+        <v>75428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkön, Mpd</t>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632751</v>
+        <v>632989</v>
       </c>
       <c r="R7" t="n">
-        <v>6898784</v>
+        <v>6898628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1255,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt på flera träd</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,60 +1290,68 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126721330</v>
+        <v>124675777</v>
       </c>
       <c r="B8" t="n">
-        <v>98477</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkön, Mpd</t>
+          <t>Ännsikslandet, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632610</v>
+        <v>633031</v>
       </c>
       <c r="R8" t="n">
-        <v>6898549</v>
+        <v>6898608</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1375,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,22 +1395,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126721324</v>
+        <v>84835064</v>
       </c>
       <c r="B9" t="n">
-        <v>98471</v>
+        <v>57144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,41 +1418,53 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkön, Mpd</t>
+          <t>Furuskärsvägen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632735</v>
+        <v>632586</v>
       </c>
       <c r="R9" t="n">
-        <v>6898744</v>
+        <v>6898727</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1443,12 +1488,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1457,29 +1512,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Rode Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Bruno Nordin, Rode Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128302733</v>
+        <v>84836043</v>
       </c>
       <c r="B10" t="n">
-        <v>92786</v>
+        <v>58393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,37 +1541,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>102999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ennsikslandet, Ennsikslandet, Mpd</t>
+          <t>Furuskärsvägen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632668</v>
+        <v>632586</v>
       </c>
       <c r="R10" t="n">
-        <v>6898566</v>
+        <v>6898727</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1541,12 +1606,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,15 +1636,837 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Bruno Nordin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>84835001</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Furuskärsvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>632586</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6898727</v>
+      </c>
+      <c r="S11" t="n">
+        <v>16</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Bruno Nordin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126721325</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>632753</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6898803</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126721324</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>632735</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6898744</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126721332</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>632751</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6898784</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126721329</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>632585</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6898509</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126721330</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>632610</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6898549</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124661344</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ännsiklandet, Ännsiklandet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>633020</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6898633</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126721331</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Björkön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>632992</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6898452</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13443-2025 artfynd.xlsx
+++ b/artfynd/A 13443-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124662148</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126721327</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124661379</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128302733</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124662316</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124661457</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124675777</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84835064</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84836043</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84835001</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1861,6 +1916,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126721325</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1963,6 +2023,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126721324</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2060,6 +2125,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126721332</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2157,6 +2227,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126721329</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2254,6 +2329,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126721330</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2370,6 +2450,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124661344</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,8 +2552,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126721331</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>